--- a/docs/literature_v4.xlsx
+++ b/docs/literature_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AdikariAdikari\PycharmProjects\ST-GNN\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6109D5-36F7-49F6-BB15-87972D9B23C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31C9B14-47FB-4EE5-8D86-35D3617D6CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51720" yWindow="10470" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="Revision log" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">General!$B$1:$B$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Architecture!$G$1:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">General!$G$1:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Graph Construction'!$A$1:$D$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Physical Constraints'!$D$1:$D$39</definedName>
   </definedNames>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2758" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="1252">
   <si>
     <t>Feature</t>
   </si>
@@ -6028,7 +6029,7 @@
       <c r="G44" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="G1:G44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7371,6 +7372,7 @@
     </row>
     <row r="42" spans="1:10" ht="187.2" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
+  <autoFilter ref="G1:G42" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="H6:I6"/>
   </mergeCells>
@@ -7380,7 +7382,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -7404,7 +7405,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>55</v>
       </c>
@@ -7432,7 +7433,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
         <v>69</v>
       </c>
@@ -7460,7 +7461,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="16" customFormat="1" ht="28.8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6" t="s">
         <v>76</v>
       </c>
@@ -7474,7 +7475,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
         <v>668</v>
       </c>
@@ -7488,7 +7489,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="19" customFormat="1" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" s="19" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
         <v>81</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="10" t="s">
         <v>86</v>
       </c>
@@ -7516,7 +7517,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
@@ -7530,7 +7531,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="8" t="s">
         <v>95</v>
       </c>
@@ -7559,7 +7560,7 @@
       </c>
       <c r="E12" s="31"/>
     </row>
-    <row r="13" spans="1:5" s="16" customFormat="1" ht="43.2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
         <v>104</v>
       </c>
@@ -7573,7 +7574,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="10" t="s">
         <v>107</v>
       </c>
@@ -7587,7 +7588,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8" t="s">
         <v>111</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
         <v>115</v>
       </c>
@@ -7615,7 +7616,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="10" t="s">
         <v>119</v>
       </c>
@@ -7629,7 +7630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8" t="s">
         <v>123</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
         <v>127</v>
       </c>
@@ -7672,7 +7673,7 @@
       </c>
       <c r="E20" s="31"/>
     </row>
-    <row r="21" spans="1:5" s="16" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="16" t="s">
         <v>135</v>
       </c>
@@ -7686,7 +7687,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="8" t="s">
         <v>140</v>
       </c>
@@ -7715,7 +7716,7 @@
       </c>
       <c r="E23" s="31"/>
     </row>
-    <row r="24" spans="1:5" s="16" customFormat="1" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" s="16" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6" t="s">
         <v>149</v>
       </c>
@@ -7729,7 +7730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="57.6" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8" t="s">
         <v>152</v>
       </c>
@@ -7743,7 +7744,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="10" customFormat="1" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" s="10" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="12" t="s">
         <v>155</v>
       </c>
@@ -7772,7 +7773,7 @@
       </c>
       <c r="E27" s="31"/>
     </row>
-    <row r="28" spans="1:5" s="16" customFormat="1" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:5" s="16" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6" t="s">
         <v>164</v>
       </c>
@@ -7786,7 +7787,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8" t="s">
         <v>169</v>
       </c>
@@ -7800,7 +7801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
         <v>171</v>
       </c>
@@ -7814,7 +7815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8" t="s">
         <v>174</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="24" customFormat="1" ht="43.2" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" s="24" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
         <v>177</v>
       </c>
@@ -7887,7 +7888,7 @@
       </c>
       <c r="E35" s="31"/>
     </row>
-    <row r="36" spans="1:5" s="16" customFormat="1" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" s="16" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8" t="s">
         <v>1010</v>
       </c>
@@ -7901,7 +7902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8" t="s">
         <v>191</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
         <v>873</v>
       </c>
@@ -7929,7 +7930,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -7943,7 +7944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="53.7" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:5" ht="53.7" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>199</v>
       </c>
@@ -7957,7 +7958,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>202</v>
       </c>
@@ -7972,17 +7973,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D41" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Census Tract (similar to mesh)"/>
-        <filter val="Mesh"/>
-        <filter val="Mesh (derived from a HEC-RAS _x000a_model)"/>
-        <filter val="Mesh cell center"/>
-        <filter val="Uniform raster cell (similar to mesh)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D41" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -8656,7 +8647,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="22.1015625" customWidth="1"/>
@@ -9012,7 +9003,7 @@
         <v>585</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -9178,24 +9169,24 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
+      <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
-      <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -9203,7 +9194,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -9211,7 +9202,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -9219,7 +9210,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -9227,7 +9218,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -9235,17 +9226,9 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
-        <v>611</v>
-      </c>
-      <c r="C67">
         <v>1</v>
       </c>
     </row>
